--- a/Upwork_Templates/5. Clinic_Orders_Enhanced (1).xlsx
+++ b/Upwork_Templates/5. Clinic_Orders_Enhanced (1).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pvipi\Desktop\VIP_GitHub\Excel_Projects\Upwork_Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EAD6F8A-6AF2-41AC-97E3-DCD6F5E04DCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A28621A-EB77-405C-8C2E-6226D0F433EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="📋 Instructions" sheetId="1" r:id="rId1"/>
